--- a/A2_Hardware/PCB_0110_01_AA/out/10_Bom/BOM_PRJ_01101_01_AAAA.xlsx
+++ b/A2_Hardware/PCB_0110_01_AA/out/10_Bom/BOM_PRJ_01101_01_AAAA.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKS\Project\isolated-usb-rs485-rs422-converter\A2_Hardware\PCB_0110_01_AA\out\10_Bom\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E79253-1B1B-490E-99D0-CC7B487528A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xmlns:d3p1="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="211" d3p1:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="211" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Information" sheetId="4" r:id="rId1"/>
@@ -18,7 +24,7 @@
     <definedName name="gTooling">#REF!</definedName>
     <definedName name="vKartAdedi">#REF!</definedName>
   </definedNames>
-  <calcPr fullPrecision="1" calcMode="auto" calcId="191029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="215">
   <si>
     <t>Variant:</t>
   </si>
@@ -689,143 +695,100 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00\ [$USD]"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="[$-C09]dd\-mmm\-yy;@"/>
     <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <color theme="1"/>
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <color theme="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <color theme="1"/>
     </font>
     <font>
       <sz val="10"/>
+      <color indexed="13"/>
       <name val="Arial"/>
       <charset val="162"/>
-      <color indexed="13"/>
     </font>
     <font>
       <sz val="10"/>
+      <color indexed="10"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <color theme="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <color indexed="10"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <charset val="162"/>
-      <color theme="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <color theme="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
+      <color indexed="10"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <color indexed="10"/>
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <charset val="162"/>
-      <color theme="1"/>
     </font>
     <font>
       <sz val="12"/>
+      <color indexed="10"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <color indexed="10"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <color theme="1"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <charset val="162"/>
-      <color theme="1"/>
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <color rgb="FF000000"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <color theme="1"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <color theme="1"/>
-    </font>
-    <font>
-      <u val="single"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <color theme="1"/>
-    </font>
-    <font>
-      <u val="single"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <color indexed="12"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
-      <patternFill patternType="none">
-        <bgColor indexed="65"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor indexed="64"/>
-        <bgColor indexed="65"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -857,12 +820,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="64"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="25">
     <border>
@@ -1179,203 +1136,206 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf xxid="0" numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf xxid="80" numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs>
-    <xf xxid="1" numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="2" numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+  <cellXfs count="67">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
     </xf>
-    <xf xxid="3" numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
     </xf>
-    <xf xxid="4" numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf xxid="5" numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf xxid="6" numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf xxid="7" numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="8" numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="9" numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="10" numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="11" numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="12" numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="13" numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="14" numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="15" numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="16" numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="17" numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf xxid="18" numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf xxid="19" numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xxid="20" numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf xxid="21" numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf xxid="22" numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf xxid="23" numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf xxid="24" numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xxid="25" numFmtId="166" fontId="5" fillId="4" borderId="7" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xxid="26" numFmtId="167" fontId="5" fillId="4" borderId="7" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xxid="27" numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="28" numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="29" numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="30" numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="31" numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="32" numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="33" numFmtId="164" fontId="10" fillId="6" borderId="13" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xxid="34" numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf xxid="35" numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xxid="36" numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf xxid="37" numFmtId="165" fontId="1" fillId="4" borderId="13" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf xxid="38" numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf xxid="39" numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf xxid="40" numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf xxid="41" numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="42" numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf xxid="43" numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf xxid="44" numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf xxid="45" numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xxid="46" numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xxid="47" numFmtId="0" fontId="11" fillId="3" borderId="15" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xxid="48" numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xxid="49" numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xxid="50" numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xxid="51" numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xxid="52" numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xxid="53" numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xxid="54" numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xxid="55" numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xxid="56" numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xxid="57" numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xxid="58" numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xxid="59" numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xxid="60" numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xxid="61" numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="62" numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf xxid="63" numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
-    <xf xxid="64" numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf xxid="65" numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf xxid="66" numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf xxid="67" numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf xxid="68" numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf xxid="69" numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf xxid="70" numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1" quotePrefix="1"/>
-    <xf xxid="71" numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1" quotePrefix="1"/>
-    <xf xxid="72" numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1" quotePrefix="1"/>
-    <xf xxid="73" numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1" quotePrefix="1"/>
-    <xf xxid="74" numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1" quotePrefix="1"/>
-    <xf xxid="75" numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1" quotePrefix="1"/>
-    <xf xxid="76" numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1" quotePrefix="1"/>
-    <xf xxid="77" numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf xxid="78" numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf xxid="79" numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf xxid="81" numFmtId="49" fontId="1" fillId="4" borderId="13" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1408,73 +1368,73 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="0"/>
-      <rgbColor rgb="FFFFFF"/>
-      <rgbColor rgb="FF0000"/>
-      <rgbColor rgb="FF00"/>
-      <rgbColor rgb="FF"/>
-      <rgbColor rgb="FFFF00"/>
-      <rgbColor rgb="FF00FF"/>
-      <rgbColor rgb="FFFF"/>
-      <rgbColor rgb="0"/>
-      <rgbColor rgb="ECE9D8"/>
-      <rgbColor rgb="0"/>
-      <rgbColor rgb="ECE9D8"/>
-      <rgbColor rgb="0"/>
-      <rgbColor rgb="FFFFFF"/>
-      <rgbColor rgb="0"/>
-      <rgbColor rgb="FFFFFF"/>
-      <rgbColor rgb="0"/>
-      <rgbColor rgb="ECE9D8"/>
-      <rgbColor rgb="0"/>
-      <rgbColor rgb="F1EFE2"/>
-      <rgbColor rgb="0"/>
-      <rgbColor rgb="8080"/>
-      <rgbColor rgb="C0C0C0"/>
-      <rgbColor rgb="808080"/>
-      <rgbColor rgb="9999FF"/>
-      <rgbColor rgb="993366"/>
-      <rgbColor rgb="FFFFCC"/>
-      <rgbColor rgb="CCFFFF"/>
-      <rgbColor rgb="660066"/>
-      <rgbColor rgb="FF8080"/>
-      <rgbColor rgb="66CC"/>
-      <rgbColor rgb="CCCCFF"/>
-      <rgbColor rgb="80"/>
-      <rgbColor rgb="FF00FF"/>
-      <rgbColor rgb="FFFF00"/>
-      <rgbColor rgb="FFFF"/>
-      <rgbColor rgb="800080"/>
-      <rgbColor rgb="800000"/>
-      <rgbColor rgb="8080"/>
-      <rgbColor rgb="FF"/>
-      <rgbColor rgb="CCFF"/>
-      <rgbColor rgb="CCFFFF"/>
-      <rgbColor rgb="CCFFCC"/>
-      <rgbColor rgb="FFFF99"/>
-      <rgbColor rgb="99CCFF"/>
-      <rgbColor rgb="FF99CC"/>
-      <rgbColor rgb="CC99FF"/>
-      <rgbColor rgb="FFCC99"/>
-      <rgbColor rgb="3366FF"/>
-      <rgbColor rgb="33CCCC"/>
-      <rgbColor rgb="99CC00"/>
-      <rgbColor rgb="FFCC00"/>
-      <rgbColor rgb="FF9900"/>
-      <rgbColor rgb="FF6600"/>
-      <rgbColor rgb="666699"/>
-      <rgbColor rgb="969696"/>
-      <rgbColor rgb="3366"/>
-      <rgbColor rgb="339966"/>
-      <rgbColor rgb="3300"/>
-      <rgbColor rgb="333300"/>
-      <rgbColor rgb="993300"/>
-      <rgbColor rgb="993366"/>
-      <rgbColor rgb="333399"/>
-      <rgbColor rgb="333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00ECE9D8"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00ECE9D8"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00ECE9D8"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00F1EFE2"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
@@ -1502,8 +1462,8 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Resim 1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <xdr:cNvPr id="2" name="Resim 1">
+          <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBD098A8-94B1-4801-88A0-60224EE2FF23}"/>
             </a:ext>
@@ -1514,8 +1474,8 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:d5p1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" d5p1:embed="rId1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
@@ -1530,11 +1490,11 @@
           <a:off x="1543050" y="1790700"/>
           <a:ext cx="907676" cy="925784"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
           <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
             <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
               <a:solidFill>
@@ -1568,7 +1528,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Resim 2">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1410B02-D79F-7765-E2A8-3B206C8B0C38}"/>
             </a:ext>
@@ -1579,8 +1539,8 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:d5p1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" d5p1:embed="rId1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
@@ -1595,141 +1555,11 @@
           <a:off x="190501" y="78441"/>
           <a:ext cx="907676" cy="925784"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>656369</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>172045</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1565188</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>1098054</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Resim 1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBD098A8-94B1-4801-88A0-60224EE2FF23}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:d5p1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" d5p1:embed="rId1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1543050" y="1790700"/>
-          <a:ext cx="907676" cy="925784"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>190453</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>79028</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>381372</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>443433</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Resim 2">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1410B02-D79F-7765-E2A8-3B206C8B0C38}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:d5p1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" d5p1:embed="rId1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="190501" y="78441"/>
-          <a:ext cx="907676" cy="925784"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
           <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
             <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
               <a:solidFill>
@@ -2031,132 +1861,131 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B10:C32"/>
-  <sheetFormatPr defaultRowHeight="12.75" baseColWidth="0"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.28125" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
     <col min="2" max="2" width="33.7109375" customWidth="1"/>
-    <col min="3" max="3" width="61.28125" customWidth="1"/>
+    <col min="3" max="3" width="61.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="10" ht="13.5" thickBot="1"/>
-    <row r="11" spans="2:3" ht="102" customHeight="1" thickBot="1">
-      <c r="B11" s="60"/>
-      <c r="C11" s="61" t="s">
+    <row r="10" spans="2:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:3" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="36"/>
+      <c r="C11" s="37" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" ht="13.5" thickBot="1"/>
-    <row r="13" spans="2:3">
-      <c r="B13" s="68" t="s">
+    <row r="12" spans="2:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B13" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="64"/>
-    </row>
-    <row r="14" spans="2:3" ht="13.5" thickBot="1">
-      <c r="B14" s="65"/>
-      <c r="C14" s="66"/>
-    </row>
-    <row r="18" ht="13.5" thickBot="1"/>
-    <row r="19" spans="2:3">
-      <c r="B19" s="23" t="s">
+      <c r="C13" s="52"/>
+    </row>
+    <row r="14" spans="2:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="53"/>
+      <c r="C14" s="54"/>
+    </row>
+    <row r="18" spans="2:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B19" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="12"/>
-    </row>
-    <row r="20" spans="2:3">
-      <c r="B20" s="24">
+      <c r="C19" s="9"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B20" s="20">
         <f ca="1">TODAY()</f>
-        <v>46300</v>
-      </c>
-      <c r="C20" s="13"/>
-    </row>
-    <row r="21" spans="2:3" ht="13.5" thickBot="1">
-      <c r="B21" s="25">
+        <v>46306</v>
+      </c>
+      <c r="C20" s="10"/>
+    </row>
+    <row r="21" spans="2:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="21">
         <f ca="1">NOW()</f>
-        <v>46300.657900486112</v>
-      </c>
-      <c r="C21" s="13"/>
-    </row>
-    <row r="22" spans="2:3" ht="15">
-      <c r="B22" s="44" t="s">
+        <v>46306.996919791665</v>
+      </c>
+      <c r="C21" s="10"/>
+    </row>
+    <row r="22" spans="2:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="B22" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="45"/>
-    </row>
-    <row r="23" spans="2:3">
+      <c r="C22" s="48"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="69" t="s">
+      <c r="C23" s="38" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="2:3">
-      <c r="B24" s="26" t="s">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B24" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="70" t="s">
+      <c r="C24" s="39" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="2:3">
-      <c r="B25" s="27" t="s">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B25" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="71" t="s">
+      <c r="C25" s="40" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="2:3">
-      <c r="B26" s="26" t="s">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B26" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="72" t="s">
+      <c r="C26" s="41" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="2:3" ht="13.5" thickBot="1">
-      <c r="B27" s="30" t="s">
+    <row r="27" spans="2:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="73" t="s">
+      <c r="C27" s="42" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="2:3" ht="13.5" thickBot="1">
-      <c r="B28" s="14"/>
-      <c r="C28" s="15"/>
-    </row>
-    <row r="29" spans="2:3" ht="15">
-      <c r="B29" s="46" t="s">
+    <row r="28" spans="2:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="11"/>
+      <c r="C28" s="12"/>
+    </row>
+    <row r="29" spans="2:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="B29" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="47"/>
-    </row>
-    <row r="30" spans="2:3">
+      <c r="C29" s="50"/>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B30" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="74" t="s">
+      <c r="C30" s="43" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="2:3">
-      <c r="B31" s="8" t="s">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B31" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="70" t="s">
+      <c r="C31" s="39" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:3" ht="13.5" thickBot="1">
-      <c r="B32" s="10" t="s">
+    <row r="32" spans="2:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="75" t="s">
+      <c r="C32" s="44" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2173,189 +2002,192 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N39"/>
-  <sheetFormatPr defaultColWidth="24.13671875" defaultRowHeight="12.75" baseColWidth="0"/>
+  <sheetFormatPr defaultColWidth="24.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="28.56640625" style="3" customWidth="1"/>
-    <col min="5" max="6" width="28.56640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="41.421875" style="1" customWidth="1"/>
-    <col min="8" max="11" width="28.56640625" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="24.13671875" style="1" customWidth="1"/>
+    <col min="2" max="4" width="28.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="47" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.42578125" style="1" customWidth="1"/>
+    <col min="8" max="11" width="28.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="24.140625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="24.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="44.25" customHeight="1">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="21" t="s">
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="76" t="s">
+      <c r="F1" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="17" t="s">
+      <c r="G1" s="62"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="77" t="s">
+      <c r="J1" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="40"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-    </row>
-    <row r="2" spans="1:13" ht="44.25" customHeight="1" thickBot="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="22" t="s">
+      <c r="K1" s="32"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+    </row>
+    <row r="2" spans="1:14" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="78" t="s">
+      <c r="F2" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="19" t="s">
+      <c r="G2" s="65"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="32"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-    </row>
-    <row r="3" spans="1:14" s="16" customFormat="1" ht="30" customHeight="1">
-      <c r="A3" s="38" t="s">
+      <c r="J2" s="25"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+    </row>
+    <row r="3" spans="1:14" s="13" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="39" t="s">
+      <c r="H3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="J3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="K3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="42" t="s">
+      <c r="L3" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="42" t="s">
+      <c r="M3" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="42" t="s">
+      <c r="N3" s="34" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A4" s="37">
+    <row r="4" spans="1:14" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="29">
         <f>ROW(A4) - ROW($A$3)</f>
         <v>1</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="34" t="s">
+      <c r="C4" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="27">
+        <v>6</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="J4" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="K4" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="L4" s="46" t="s">
+        <v>186</v>
+      </c>
+      <c r="M4" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="N4" s="33" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="29">
+        <f>ROW(A5) - ROW($A$3)</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="H5" s="27">
         <v>1</v>
       </c>
-      <c r="G4" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="H4" s="34">
-        <v>1</v>
-      </c>
-      <c r="I4" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="J4" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="K4" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="L4" s="79" t="s">
-        <v>183</v>
-      </c>
-      <c r="M4" s="41" t="s">
-        <v>212</v>
-      </c>
-      <c r="N4" s="41" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="30" customHeight="1">
-      <c r="A5" s="37">
-        <f t="shared" si="0" ref="A5:A34">ROW(A5) - ROW($A$3)</f>
-        <v>2</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="G5" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="H5" s="34">
-        <v>2</v>
-      </c>
-      <c r="I5" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="J5" s="35" t="s">
-        <v>152</v>
+      <c r="I5" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>164</v>
       </c>
       <c r="K5" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="L5" s="79" t="s">
-        <v>184</v>
+      <c r="L5" s="46" t="s">
+        <v>195</v>
       </c>
       <c r="M5" s="33" t="s">
         <v>212</v>
@@ -2364,268 +2196,268 @@
         <v>214</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="30" customHeight="1">
-      <c r="A6" s="37">
+    <row r="6" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="29">
         <f>ROW(A6) - ROW($A$3)</f>
         <v>3</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="H6" s="34">
-        <v>1</v>
-      </c>
-      <c r="I6" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="J6" s="35" t="s">
-        <v>153</v>
-      </c>
-      <c r="K6" s="41" t="s">
+      <c r="C6" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="H6" s="27">
+        <v>2</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="K6" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="L6" s="79" t="s">
-        <v>185</v>
-      </c>
-      <c r="M6" s="41" t="s">
+      <c r="L6" s="46" t="s">
+        <v>196</v>
+      </c>
+      <c r="M6" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="N6" s="41" t="s">
+      <c r="N6" s="26" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="30" customHeight="1">
-      <c r="A7" s="37">
+    <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="29">
         <f>ROW(A7) - ROW($A$3)</f>
         <v>4</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="H7" s="34">
+      <c r="C7" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="H7" s="27">
         <v>1</v>
       </c>
-      <c r="I7" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="J7" s="35" t="s">
-        <v>136</v>
+      <c r="I7" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>168</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="L7" s="79" t="s">
-        <v>136</v>
+        <v>181</v>
+      </c>
+      <c r="L7" s="46" t="s">
+        <v>199</v>
       </c>
       <c r="M7" s="33" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N7" s="33" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="30" customHeight="1">
-      <c r="A8" s="37">
+    <row r="8" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="29">
         <f>ROW(A8) - ROW($A$3)</f>
         <v>5</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="41" t="s">
+      <c r="C8" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="H8" s="34">
-        <v>6</v>
-      </c>
-      <c r="I8" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="J8" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="K8" s="41" t="s">
+      <c r="F8" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="H8" s="27">
+        <v>5</v>
+      </c>
+      <c r="I8" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="K8" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="L8" s="79" t="s">
-        <v>186</v>
-      </c>
-      <c r="M8" s="41" t="s">
+      <c r="L8" s="46" t="s">
+        <v>211</v>
+      </c>
+      <c r="M8" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="N8" s="41" t="s">
+      <c r="N8" s="33" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="30" customHeight="1">
-      <c r="A9" s="37">
+    <row r="9" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="29">
         <f>ROW(A9) - ROW($A$3)</f>
         <v>6</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="H9" s="34">
+      <c r="C9" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="H9" s="27">
         <v>2</v>
       </c>
-      <c r="I9" s="35" t="s">
+      <c r="I9" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="J9" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="K9" s="33" t="s">
+      <c r="J9" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="K9" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="L9" s="79" t="s">
-        <v>187</v>
-      </c>
-      <c r="M9" s="33" t="s">
+      <c r="L9" s="46" t="s">
+        <v>184</v>
+      </c>
+      <c r="M9" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="N9" s="33" t="s">
+      <c r="N9" s="26" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="30" customHeight="1">
-      <c r="A10" s="37">
+    <row r="10" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="29">
         <f>ROW(A10) - ROW($A$3)</f>
         <v>7</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="H10" s="34">
-        <v>4</v>
-      </c>
-      <c r="I10" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="J10" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="K10" s="41" t="s">
+      <c r="C10" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="H10" s="27">
+        <v>1</v>
+      </c>
+      <c r="I10" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="K10" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="L10" s="79" t="s">
-        <v>188</v>
-      </c>
-      <c r="M10" s="41" t="s">
+      <c r="L10" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="M10" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="N10" s="41" t="s">
+      <c r="N10" s="33" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="30" customHeight="1">
-      <c r="A11" s="37">
+    <row r="11" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="29">
         <f>ROW(A11) - ROW($A$3)</f>
         <v>8</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="G11" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="H11" s="34">
-        <v>2</v>
-      </c>
-      <c r="I11" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="J11" s="35" t="s">
-        <v>157</v>
+      <c r="C11" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="H11" s="27">
+        <v>1</v>
+      </c>
+      <c r="I11" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>170</v>
       </c>
       <c r="K11" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="L11" s="79" t="s">
-        <v>189</v>
+      <c r="L11" s="46" t="s">
+        <v>201</v>
       </c>
       <c r="M11" s="33" t="s">
         <v>212</v>
@@ -2634,178 +2466,176 @@
         <v>214</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="30" customHeight="1">
-      <c r="A12" s="37">
+    <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="29">
         <f>ROW(A12) - ROW($A$3)</f>
         <v>9</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="G12" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="H12" s="34">
-        <v>2</v>
-      </c>
-      <c r="I12" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="J12" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="K12" s="41" t="s">
+      <c r="C12" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="H12" s="27">
+        <v>1</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="K12" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="L12" s="79" t="s">
-        <v>158</v>
-      </c>
-      <c r="M12" s="41" t="s">
+      <c r="L12" s="46" t="s">
+        <v>207</v>
+      </c>
+      <c r="M12" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="N12" s="41" t="s">
+      <c r="N12" s="33" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="30" customHeight="1">
-      <c r="A13" s="37">
+    <row r="13" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="29">
         <f>ROW(A13) - ROW($A$3)</f>
         <v>10</v>
       </c>
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="H13" s="34">
+      <c r="C13" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="H13" s="27">
         <v>2</v>
       </c>
-      <c r="I13" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="J13" s="35" t="s">
-        <v>159</v>
-      </c>
-      <c r="K13" s="33" t="s">
+      <c r="I13" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="K13" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="L13" s="79" t="s">
-        <v>190</v>
-      </c>
-      <c r="M13" s="33" t="s">
+      <c r="L13" s="46" t="s">
+        <v>208</v>
+      </c>
+      <c r="M13" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="N13" s="33" t="s">
+      <c r="N13" s="26" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="30" customHeight="1">
-      <c r="A14" s="37">
+    <row r="14" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="29">
         <f>ROW(A14) - ROW($A$3)</f>
         <v>11</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="G14" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="H14" s="34">
-        <v>2</v>
-      </c>
-      <c r="I14" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="J14" s="35" t="s">
-        <v>160</v>
-      </c>
-      <c r="K14" s="41" t="s">
+      <c r="C14" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="H14" s="27">
+        <v>1</v>
+      </c>
+      <c r="I14" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="J14" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="K14" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="L14" s="79" t="s">
-        <v>191</v>
-      </c>
-      <c r="M14" s="41" t="s">
+      <c r="L14" s="46" t="s">
+        <v>209</v>
+      </c>
+      <c r="M14" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="N14" s="41" t="s">
+      <c r="N14" s="33" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="30" customHeight="1">
-      <c r="A15" s="37">
+    <row r="15" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="29">
         <f>ROW(A15) - ROW($A$3)</f>
         <v>12</v>
       </c>
-      <c r="B15" s="34" t="s">
+      <c r="B15" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="43" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="F15" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="H15" s="34">
-        <v>2</v>
-      </c>
-      <c r="I15" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="J15" s="35" t="s">
-        <v>161</v>
+      <c r="C15" s="27"/>
+      <c r="D15" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" s="27">
+        <v>1</v>
+      </c>
+      <c r="I15" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="J15" s="28" t="s">
+        <v>151</v>
       </c>
       <c r="K15" s="33" t="s">
-        <v>182</v>
-      </c>
-      <c r="L15" s="79" t="s">
-        <v>192</v>
+        <v>181</v>
+      </c>
+      <c r="L15" s="46" t="s">
+        <v>183</v>
       </c>
       <c r="M15" s="33" t="s">
         <v>212</v>
@@ -2814,538 +2644,538 @@
         <v>214</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="30" customHeight="1">
-      <c r="A16" s="37">
+    <row r="16" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="29">
         <f>ROW(A16) - ROW($A$3)</f>
         <v>13</v>
       </c>
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="G16" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="H16" s="34">
-        <v>4</v>
-      </c>
-      <c r="I16" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="J16" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="K16" s="41" t="s">
-        <v>182</v>
-      </c>
-      <c r="L16" s="79" t="s">
-        <v>193</v>
-      </c>
-      <c r="M16" s="41" t="s">
+      <c r="D16" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="H16" s="27">
+        <v>2</v>
+      </c>
+      <c r="I16" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="J16" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="K16" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="L16" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="M16" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="N16" s="41" t="s">
+      <c r="N16" s="26" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="30" customHeight="1">
-      <c r="A17" s="37">
+    <row r="17" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="29">
         <f>ROW(A17) - ROW($A$3)</f>
         <v>14</v>
       </c>
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="G17" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="H17" s="34">
-        <v>2</v>
-      </c>
-      <c r="I17" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="J17" s="35" t="s">
-        <v>163</v>
-      </c>
-      <c r="K17" s="33" t="s">
+      <c r="C17" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17" s="27">
+        <v>1</v>
+      </c>
+      <c r="I17" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="J17" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="K17" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="L17" s="79" t="s">
-        <v>194</v>
-      </c>
-      <c r="M17" s="33" t="s">
+      <c r="L17" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="M17" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="N17" s="33" t="s">
+      <c r="N17" s="26" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="30" customHeight="1">
-      <c r="A18" s="37">
+    <row r="18" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="29">
         <f>ROW(A18) - ROW($A$3)</f>
         <v>15</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="G18" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="H18" s="34">
+      <c r="C18" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="27">
         <v>1</v>
       </c>
-      <c r="I18" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="J18" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="K18" s="41" t="s">
+      <c r="I18" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="J18" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="K18" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="L18" s="79" t="s">
-        <v>195</v>
-      </c>
-      <c r="M18" s="41" t="s">
+      <c r="L18" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="M18" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="N18" s="41" t="s">
+      <c r="N18" s="33" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="30" customHeight="1">
-      <c r="A19" s="37">
+    <row r="19" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="29">
         <f>ROW(A19) - ROW($A$3)</f>
         <v>16</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="43" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="G19" s="34" t="s">
-        <v>117</v>
-      </c>
-      <c r="H19" s="34">
+      <c r="C19" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="H19" s="27">
         <v>2</v>
       </c>
-      <c r="I19" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="J19" s="35" t="s">
-        <v>165</v>
-      </c>
-      <c r="K19" s="33" t="s">
+      <c r="I19" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="J19" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="K19" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="L19" s="79" t="s">
-        <v>196</v>
-      </c>
-      <c r="M19" s="33" t="s">
+      <c r="L19" s="46" t="s">
+        <v>187</v>
+      </c>
+      <c r="M19" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="N19" s="33" t="s">
+      <c r="N19" s="26" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="30" customHeight="1">
-      <c r="A20" s="37">
+    <row r="20" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="29">
         <f>ROW(A20) - ROW($A$3)</f>
         <v>17</v>
       </c>
-      <c r="B20" s="34" t="s">
+      <c r="B20" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="E20" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F20" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="H20" s="34">
+      <c r="C20" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="H20" s="27">
         <v>2</v>
       </c>
-      <c r="I20" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="J20" s="35" t="s">
-        <v>166</v>
-      </c>
-      <c r="K20" s="41" t="s">
+      <c r="I20" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="J20" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="K20" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="L20" s="79" t="s">
-        <v>197</v>
-      </c>
-      <c r="M20" s="41" t="s">
+      <c r="L20" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="M20" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="N20" s="41" t="s">
+      <c r="N20" s="33" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="30" customHeight="1">
-      <c r="A21" s="37">
+    <row r="21" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="29">
         <f>ROW(A21) - ROW($A$3)</f>
         <v>18</v>
       </c>
-      <c r="B21" s="34" t="s">
+      <c r="B21" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F21" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="G21" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="H21" s="34">
-        <v>4</v>
-      </c>
-      <c r="I21" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="J21" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="K21" s="33" t="s">
+      <c r="C21" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="G21" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="H21" s="27">
+        <v>2</v>
+      </c>
+      <c r="I21" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="J21" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="K21" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="L21" s="79" t="s">
-        <v>198</v>
-      </c>
-      <c r="M21" s="33" t="s">
+      <c r="L21" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="M21" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="N21" s="33" t="s">
+      <c r="N21" s="26" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="30" customHeight="1">
-      <c r="A22" s="37">
+    <row r="22" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="29">
         <f>ROW(A22) - ROW($A$3)</f>
         <v>19</v>
       </c>
-      <c r="B22" s="34" t="s">
+      <c r="B22" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="F22" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="G22" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="H22" s="34">
+      <c r="D22" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="H22" s="27">
         <v>1</v>
       </c>
-      <c r="I22" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="J22" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="K22" s="41" t="s">
+      <c r="I22" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="J22" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="K22" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="L22" s="79" t="s">
-        <v>199</v>
-      </c>
-      <c r="M22" s="41" t="s">
+      <c r="L22" s="46" t="s">
+        <v>205</v>
+      </c>
+      <c r="M22" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="N22" s="41" t="s">
+      <c r="N22" s="33" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="30" customHeight="1">
-      <c r="A23" s="37">
+    <row r="23" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="29">
         <f>ROW(A23) - ROW($A$3)</f>
         <v>20</v>
       </c>
-      <c r="B23" s="34" t="s">
+      <c r="B23" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="E23" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="H23" s="34">
-        <v>4</v>
-      </c>
-      <c r="I23" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="J23" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="K23" s="33" t="s">
+      <c r="D23" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="H23" s="27">
+        <v>1</v>
+      </c>
+      <c r="I23" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="J23" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="K23" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="L23" s="79" t="s">
-        <v>200</v>
-      </c>
-      <c r="M23" s="33" t="s">
+      <c r="L23" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="M23" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="N23" s="33" t="s">
+      <c r="N23" s="26" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="30" customHeight="1">
-      <c r="A24" s="37">
+    <row r="24" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="29">
         <f>ROW(A24) - ROW($A$3)</f>
         <v>21</v>
       </c>
-      <c r="B24" s="34" t="s">
+      <c r="B24" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="F24" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="G24" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="H24" s="34">
+      <c r="C24" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="H24" s="27">
         <v>1</v>
       </c>
-      <c r="I24" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="J24" s="35" t="s">
-        <v>170</v>
-      </c>
-      <c r="K24" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="L24" s="79" t="s">
-        <v>201</v>
-      </c>
-      <c r="M24" s="41" t="s">
-        <v>212</v>
-      </c>
-      <c r="N24" s="41" t="s">
+      <c r="I24" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="J24" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="K24" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="L24" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="M24" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="N24" s="26" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="30" customHeight="1">
-      <c r="A25" s="37">
+    <row r="25" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="29">
         <f>ROW(A25) - ROW($A$3)</f>
         <v>22</v>
       </c>
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="E25" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="G25" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="H25" s="34">
-        <v>1</v>
-      </c>
-      <c r="I25" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="J25" s="35" t="s">
-        <v>171</v>
-      </c>
-      <c r="K25" s="33" t="s">
+      <c r="D25" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="G25" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="H25" s="27">
+        <v>4</v>
+      </c>
+      <c r="I25" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="J25" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="K25" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="L25" s="79" t="s">
-        <v>202</v>
-      </c>
-      <c r="M25" s="33" t="s">
-        <v>212</v>
-      </c>
-      <c r="N25" s="33" t="s">
+      <c r="L25" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="M25" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="N25" s="26" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="30" customHeight="1">
-      <c r="A26" s="37">
+    <row r="26" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="29">
         <f>ROW(A26) - ROW($A$3)</f>
         <v>23</v>
       </c>
-      <c r="B26" s="34" t="s">
+      <c r="B26" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="F26" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="G26" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="H26" s="34">
-        <v>1</v>
-      </c>
-      <c r="I26" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="J26" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="K26" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="L26" s="79" t="s">
-        <v>203</v>
-      </c>
-      <c r="M26" s="41" t="s">
+      <c r="C26" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="H26" s="27">
+        <v>2</v>
+      </c>
+      <c r="I26" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="J26" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="K26" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="L26" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="M26" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="N26" s="41" t="s">
+      <c r="N26" s="26" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="30" customHeight="1">
-      <c r="A27" s="37">
+    <row r="27" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="29">
         <f>ROW(A27) - ROW($A$3)</f>
         <v>24</v>
       </c>
-      <c r="B27" s="34" t="s">
+      <c r="B27" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="G27" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="H27" s="34">
-        <v>1</v>
-      </c>
-      <c r="I27" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="J27" s="35" t="s">
-        <v>173</v>
+      <c r="C27" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="G27" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="H27" s="27">
+        <v>4</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="J27" s="28" t="s">
+        <v>162</v>
       </c>
       <c r="K27" s="33" t="s">
-        <v>181</v>
-      </c>
-      <c r="L27" s="79" t="s">
-        <v>204</v>
+        <v>182</v>
+      </c>
+      <c r="L27" s="46" t="s">
+        <v>193</v>
       </c>
       <c r="M27" s="33" t="s">
         <v>212</v>
@@ -3354,178 +3184,178 @@
         <v>214</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="30" customHeight="1">
-      <c r="A28" s="37">
+    <row r="28" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="29">
         <f>ROW(A28) - ROW($A$3)</f>
         <v>25</v>
       </c>
-      <c r="B28" s="34" t="s">
+      <c r="B28" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="E28" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="F28" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="G28" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="H28" s="34">
-        <v>1</v>
-      </c>
-      <c r="I28" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="J28" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="K28" s="41" t="s">
+      <c r="C28" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F28" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="H28" s="27">
+        <v>4</v>
+      </c>
+      <c r="I28" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="J28" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="K28" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="L28" s="79" t="s">
-        <v>205</v>
-      </c>
-      <c r="M28" s="41" t="s">
+      <c r="L28" s="46" t="s">
+        <v>188</v>
+      </c>
+      <c r="M28" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="N28" s="41" t="s">
+      <c r="N28" s="33" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="30" customHeight="1">
-      <c r="A29" s="37">
+    <row r="29" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="29">
         <f>ROW(A29) - ROW($A$3)</f>
         <v>26</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="E29" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="F29" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="G29" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="H29" s="34">
-        <v>1</v>
-      </c>
-      <c r="I29" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="J29" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="K29" s="33" t="s">
+      <c r="C29" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="G29" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="H29" s="27">
+        <v>2</v>
+      </c>
+      <c r="I29" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="J29" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="K29" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="L29" s="79" t="s">
-        <v>206</v>
-      </c>
-      <c r="M29" s="33" t="s">
+      <c r="L29" s="46" t="s">
+        <v>189</v>
+      </c>
+      <c r="M29" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="N29" s="33" t="s">
+      <c r="N29" s="26" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="30" customHeight="1">
-      <c r="A30" s="37">
+    <row r="30" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="29">
         <f>ROW(A30) - ROW($A$3)</f>
         <v>27</v>
       </c>
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="F30" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="G30" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H30" s="34">
-        <v>1</v>
-      </c>
-      <c r="I30" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="J30" s="35" t="s">
-        <v>176</v>
-      </c>
-      <c r="K30" s="41" t="s">
+      <c r="C30" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F30" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="G30" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="H30" s="27">
+        <v>2</v>
+      </c>
+      <c r="I30" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="J30" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="K30" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="L30" s="79" t="s">
-        <v>207</v>
-      </c>
-      <c r="M30" s="41" t="s">
+      <c r="L30" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="M30" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="N30" s="41" t="s">
+      <c r="N30" s="33" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="30" customHeight="1">
-      <c r="A31" s="37">
+    <row r="31" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="29">
         <f>ROW(A31) - ROW($A$3)</f>
         <v>28</v>
       </c>
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="F31" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="G31" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="H31" s="34">
+      <c r="D31" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F31" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="H31" s="27">
         <v>2</v>
       </c>
-      <c r="I31" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="J31" s="35" t="s">
-        <v>177</v>
+      <c r="I31" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="J31" s="28" t="s">
+        <v>166</v>
       </c>
       <c r="K31" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="L31" s="79" t="s">
-        <v>208</v>
+      <c r="L31" s="46" t="s">
+        <v>197</v>
       </c>
       <c r="M31" s="33" t="s">
         <v>212</v>
@@ -3534,142 +3364,142 @@
         <v>214</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="30" customHeight="1">
-      <c r="A32" s="37">
+    <row r="32" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="29">
         <f>ROW(A32) - ROW($A$3)</f>
         <v>29</v>
       </c>
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="34" t="s">
+      <c r="C32" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D32" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="E32" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="F32" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="G32" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="H32" s="34">
-        <v>1</v>
-      </c>
-      <c r="I32" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="J32" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="K32" s="41" t="s">
+      <c r="D32" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F32" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="H32" s="27">
+        <v>4</v>
+      </c>
+      <c r="I32" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="J32" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="K32" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="L32" s="79" t="s">
-        <v>209</v>
-      </c>
-      <c r="M32" s="41" t="s">
+      <c r="L32" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="M32" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="N32" s="41" t="s">
+      <c r="N32" s="26" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="30" customHeight="1">
-      <c r="A33" s="37">
+    <row r="33" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="29">
         <f>ROW(A33) - ROW($A$3)</f>
         <v>30</v>
       </c>
-      <c r="B33" s="34" t="s">
+      <c r="B33" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D33" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="E33" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="F33" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="G33" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="H33" s="34">
+      <c r="D33" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F33" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="G33" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="H33" s="27">
         <v>4</v>
       </c>
-      <c r="I33" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="J33" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="K33" s="33" t="s">
+      <c r="I33" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="J33" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="K33" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="L33" s="79" t="s">
-        <v>210</v>
-      </c>
-      <c r="M33" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="N33" s="33" t="s">
+      <c r="L33" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="M33" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="N33" s="26" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="30" customHeight="1">
-      <c r="A34" s="37">
+    <row r="34" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="29">
         <f>ROW(A34) - ROW($A$3)</f>
         <v>31</v>
       </c>
-      <c r="B34" s="34" t="s">
+      <c r="B34" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="D34" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="F34" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="G34" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="H34" s="34">
-        <v>5</v>
-      </c>
-      <c r="I34" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="J34" s="35" t="s">
-        <v>180</v>
-      </c>
-      <c r="K34" s="41" t="s">
+      <c r="C34" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="F34" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="G34" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="H34" s="27">
+        <v>1</v>
+      </c>
+      <c r="I34" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="J34" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="K34" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="L34" s="79" t="s">
-        <v>211</v>
-      </c>
-      <c r="M34" s="41" t="s">
+      <c r="L34" s="46" t="s">
+        <v>204</v>
+      </c>
+      <c r="M34" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="N34" s="41" t="s">
+      <c r="N34" s="26" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="30" customHeight="1">
+    <row r="35" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -3683,45 +3513,49 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="14:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N39"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N3"/>
+  <autoFilter ref="A3:N3" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:N35">
+      <sortCondition ref="D3"/>
+    </sortState>
+  </autoFilter>
   <mergeCells count="3">
     <mergeCell ref="A1:D2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="F2:H2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:C5 E4:J5 B34:C34 E34:J34">
-    <cfRule type="expression" dxfId="3" stopIfTrue="1" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3" stopIfTrue="1">
       <formula>#REF!=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" stopIfTrue="1" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4" stopIfTrue="1">
+      <formula>-#REF!&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:C33 E6:J33">
+    <cfRule type="expression" dxfId="5" priority="5" stopIfTrue="1">
+      <formula>#REF!=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="5" stopIfTrue="1">
       <formula>-#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:L5 L34">
-    <cfRule type="expression" dxfId="1" stopIfTrue="1" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>#REF!=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" stopIfTrue="1" priority="2">
-      <formula>-#REF!&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6:C33 E6:J33">
-    <cfRule type="expression" dxfId="3" stopIfTrue="1" priority="3">
-      <formula>#REF!=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" stopIfTrue="1" priority="4">
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
       <formula>-#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L33">
-    <cfRule type="expression" dxfId="1" stopIfTrue="1" priority="1">
+    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
       <formula>#REF!=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" stopIfTrue="1" priority="2">
+    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
       <formula>-#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
